--- a/hourly datasets/cap_gen_year14final.xlsx
+++ b/hourly datasets/cap_gen_year14final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1034266086838253</v>
+        <v>0.1004892525445823</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1006472130890178</v>
+        <v>0.0970711581578164</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2040738217728431</v>
+        <v>0.1975604107023987</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09232867143567874</v>
+        <v>0.08688622264484544</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1957552801195041</v>
+        <v>0.1873754751894278</v>
       </c>
     </row>
     <row r="5">
@@ -531,15 +531,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05631367723607251</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+        <v>0.04589653303170025</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.002411474412039346</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12.10260051116404</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.02983736834619446</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04115196726730635</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05064109879609337</v>
+      </c>
       <c r="H5" t="n">
-        <v>0.1597402859198978</v>
+        <v>0.1463857855762826</v>
       </c>
     </row>
     <row r="6">
@@ -549,25 +559,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05061628046209641</v>
+        <v>0.03582217487452128</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002775124116460936</v>
+        <v>0.001842181333823431</v>
       </c>
       <c r="D6" t="n">
-        <v>7.229908160878246</v>
+        <v>5.815611332136209</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01722574224865763</v>
+        <v>0.01262412892690017</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04516223503779269</v>
+        <v>0.03219800531880384</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05607032588640019</v>
+        <v>0.03944634443023773</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1540428891459217</v>
+        <v>0.1363114274191036</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +587,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04756014946787813</v>
+        <v>0.02766228454924267</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -585,7 +595,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.1509867581517035</v>
+        <v>0.128151537093825</v>
       </c>
     </row>
     <row r="8">
@@ -595,25 +605,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03583754662207645</v>
+        <v>0.006547335284480371</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002786738962805749</v>
+        <v>0.001354784762765694</v>
       </c>
       <c r="D8" t="n">
-        <v>4.940510280842267</v>
+        <v>2.013106596332452</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006472974945438711</v>
+        <v>0.003828133865236785</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03035778965654701</v>
+        <v>0.003875961378623792</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0413173035876058</v>
+        <v>0.009218709190336922</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1392641553059018</v>
+        <v>0.1070365878290627</v>
       </c>
     </row>
     <row r="9">
@@ -623,25 +633,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03686871014905553</v>
+        <v>0.005663458081302438</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001845062320910928</v>
+        <v>0.0004038476786903112</v>
       </c>
       <c r="D9" t="n">
-        <v>5.227821554341242</v>
+        <v>2.007801262857778</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006808002356149154</v>
+        <v>0.003200069840291781</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03324792020700708</v>
+        <v>0.004870232732261207</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04048950009110399</v>
+        <v>0.006456683430343787</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1402953188328809</v>
+        <v>0.1061527106258848</v>
       </c>
     </row>
     <row r="10">
@@ -651,25 +661,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03901001682294634</v>
+        <v>0.00538792202197559</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00255422690986017</v>
+        <v>0.001322432247090697</v>
       </c>
       <c r="D10" t="n">
-        <v>5.773535046456106</v>
+        <v>1.446163236959488</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007460108337300352</v>
+        <v>0.001607492108426603</v>
       </c>
       <c r="F10" t="n">
-        <v>0.033988306969606</v>
+        <v>0.002780996212260872</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04403172667628798</v>
+        <v>0.007994847831690067</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1424366255067717</v>
+        <v>0.1058771745665579</v>
       </c>
     </row>
     <row r="11">
@@ -679,7 +689,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03088017471332317</v>
+        <v>0.02976530646511861</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -687,7 +697,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1343067833971485</v>
+        <v>0.130254559009701</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +707,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05147464369771785</v>
+        <v>0.04905868056158597</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -705,7 +715,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1549012523815432</v>
+        <v>0.1495479331061683</v>
       </c>
     </row>
     <row r="13">
@@ -715,7 +725,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0677617951436638</v>
+        <v>0.06538359255139212</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -723,7 +733,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1711884038274891</v>
+        <v>0.1658728450959744</v>
       </c>
     </row>
     <row r="14">
@@ -733,7 +743,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07175102020736146</v>
+        <v>0.07006202855810219</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -741,7 +751,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1751776288911868</v>
+        <v>0.1705512811026845</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +761,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07907745582211108</v>
+        <v>0.07633087236257265</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -759,7 +769,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1825040645059364</v>
+        <v>0.176820124907155</v>
       </c>
     </row>
     <row r="16">
@@ -769,7 +779,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0837079406595235</v>
+        <v>0.08097886877138172</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -777,7 +787,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1871345493433488</v>
+        <v>0.1814681213159641</v>
       </c>
     </row>
     <row r="17">
@@ -787,7 +797,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08589609529377445</v>
+        <v>0.0836219187512979</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -795,7 +805,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1893227039775998</v>
+        <v>0.1841111712958802</v>
       </c>
     </row>
     <row r="18">
@@ -805,7 +815,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1034266086838253</v>
+        <v>-0.1004892525445823</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
@@ -823,7 +833,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08815766389767526</v>
+        <v>0.08599450627814624</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -831,7 +841,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1915842725815006</v>
+        <v>0.1864837588227286</v>
       </c>
     </row>
     <row r="20">
@@ -841,7 +851,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.09190117280910687</v>
+        <v>0.08933997365639915</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -849,7 +859,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1953277814929322</v>
+        <v>0.1898292262009815</v>
       </c>
     </row>
     <row r="21">
@@ -859,7 +869,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.09583652875897439</v>
+        <v>0.09315002448509374</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -867,7 +877,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1992631374427997</v>
+        <v>0.1936392770296761</v>
       </c>
     </row>
     <row r="22">
@@ -877,25 +887,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1000847894830573</v>
+        <v>0.0971558510159143</v>
       </c>
       <c r="C22" t="n">
-        <v>0.007506695754597443</v>
+        <v>0.00712795973837118</v>
       </c>
       <c r="D22" t="n">
-        <v>24.23474978223476</v>
+        <v>24.00303453052241</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04219457408128865</v>
+        <v>0.04304788334237448</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08530715130748218</v>
+        <v>0.08314390120397999</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1148624276586325</v>
+        <v>0.1111678008278485</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2035113981668826</v>
+        <v>0.1976451035604966</v>
       </c>
     </row>
     <row r="23">
@@ -905,25 +915,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1036830179220661</v>
+        <v>0.1010050028406189</v>
       </c>
       <c r="C23" t="n">
-        <v>0.007398999447646707</v>
+        <v>0.006997983110107142</v>
       </c>
       <c r="D23" t="n">
-        <v>25.16679227113135</v>
+        <v>25.04201334668982</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03962144289720126</v>
+        <v>0.03855730116383704</v>
       </c>
       <c r="F23" t="n">
-        <v>0.08913937494315255</v>
+        <v>0.08725576945402201</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1182266609009801</v>
+        <v>0.1147542362272157</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2071096266058914</v>
+        <v>0.2014942553852013</v>
       </c>
     </row>
     <row r="24">
@@ -933,25 +943,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1091933794225123</v>
+        <v>0.1066304509128086</v>
       </c>
       <c r="C24" t="n">
-        <v>0.007456009891838536</v>
+        <v>0.007222545988216703</v>
       </c>
       <c r="D24" t="n">
-        <v>26.78362469229936</v>
+        <v>26.73009094960385</v>
       </c>
       <c r="E24" t="n">
-        <v>0.04507251405913407</v>
+        <v>0.04262428682460107</v>
       </c>
       <c r="F24" t="n">
-        <v>0.09452914025756412</v>
+        <v>0.09243793987925054</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1238576185874605</v>
+        <v>0.1208229619463669</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2126199881063376</v>
+        <v>0.2071197034573909</v>
       </c>
     </row>
     <row r="25">
@@ -961,25 +971,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.110467683033059</v>
+        <v>0.1076398297490284</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008766470598799106</v>
+        <v>0.008307559260876866</v>
       </c>
       <c r="D25" t="n">
-        <v>25.59246074959471</v>
+        <v>25.61670857916938</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04161387311213175</v>
+        <v>0.04205968895953646</v>
       </c>
       <c r="F25" t="n">
-        <v>0.09320792228469538</v>
+        <v>0.09129675793533726</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1277274437814231</v>
+        <v>0.1239829015627198</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2138942917168843</v>
+        <v>0.2081290822936108</v>
       </c>
     </row>
     <row r="26">
@@ -989,25 +999,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.111458949772634</v>
+        <v>0.1094117248417065</v>
       </c>
       <c r="C26" t="n">
-        <v>0.008365031793420543</v>
+        <v>0.008106918617836153</v>
       </c>
       <c r="D26" t="n">
-        <v>25.75841447348996</v>
+        <v>25.88901328842088</v>
       </c>
       <c r="E26" t="n">
-        <v>0.03879307820635577</v>
+        <v>0.0384221969316984</v>
       </c>
       <c r="F26" t="n">
-        <v>0.09501340980857417</v>
+        <v>0.09347302760122432</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1279044897366938</v>
+        <v>0.1253504220821886</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2148855584564593</v>
+        <v>0.2099009773862889</v>
       </c>
     </row>
     <row r="27">
@@ -1017,25 +1027,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1118534318178833</v>
+        <v>0.1095168507379396</v>
       </c>
       <c r="C27" t="n">
-        <v>0.007433828465952445</v>
+        <v>0.007016451903546652</v>
       </c>
       <c r="D27" t="n">
-        <v>25.10410679833312</v>
+        <v>25.32383093340588</v>
       </c>
       <c r="E27" t="n">
-        <v>0.05196740885247918</v>
+        <v>0.0504331333752961</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09724637480122314</v>
+        <v>0.09572981411537045</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1264604888345434</v>
+        <v>0.1233038873605092</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2152800405017086</v>
+        <v>0.2100061032825219</v>
       </c>
     </row>
     <row r="28">
@@ -1045,25 +1055,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.108244377125806</v>
+        <v>0.1064955311289398</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007414605910322103</v>
+        <v>0.00690404387163713</v>
       </c>
       <c r="D28" t="n">
-        <v>24.00407113535745</v>
+        <v>24.26027339296263</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08279491930408636</v>
+        <v>0.08032228576350661</v>
       </c>
       <c r="F28" t="n">
-        <v>0.09367797055066414</v>
+        <v>0.09293077381063959</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1228107837009481</v>
+        <v>0.1200602884472404</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2116709858096313</v>
+        <v>0.2069847836735222</v>
       </c>
     </row>
     <row r="29">
@@ -1073,25 +1083,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.04238876528774297</v>
+        <v>0.005810623435058298</v>
       </c>
       <c r="C29" t="n">
-        <v>0.002351870200783593</v>
+        <v>0.0009589797129460442</v>
       </c>
       <c r="D29" t="n">
-        <v>6.994076770040634</v>
+        <v>1.883611970712138</v>
       </c>
       <c r="E29" t="n">
-        <v>0.006103438735143013</v>
+        <v>0.00338551360650741</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03776587826790539</v>
+        <v>0.003920490647035675</v>
       </c>
       <c r="G29" t="n">
-        <v>0.04701165230758043</v>
+        <v>0.007700756223080829</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1458153739715683</v>
+        <v>0.1062998759796406</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year14final.xlsx
+++ b/hourly datasets/cap_gen_year14final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2272932460729697</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1004892525445823</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.09906874652738687</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0970711581578164</v>
+        <v>0.384503388793308</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1975604107023987</v>
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2562788892477251</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08688622264484544</v>
+        <v>0.3643652287663445</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1873754751894278</v>
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2361407292207616</v>
       </c>
     </row>
     <row r="5">
@@ -531,25 +545,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04589653303170025</v>
+        <v>0.3693951005121576</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002411474412039346</v>
+        <v>0.003691033147568658</v>
       </c>
       <c r="D5" t="n">
-        <v>12.10260051116404</v>
+        <v>45.11544607177867</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02983736834619446</v>
+        <v>0.03281657930212895</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04115196726730635</v>
+        <v>0.1144735493703238</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05064109879609337</v>
+        <v>0.1289830991238849</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1463857855762826</v>
+        <v>16</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2411706009665747</v>
       </c>
     </row>
     <row r="6">
@@ -559,25 +576,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03582217487452128</v>
+        <v>0.4767131625716401</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001842181333823431</v>
+        <v>0.0076371658940599</v>
       </c>
       <c r="D6" t="n">
-        <v>5.815611332136209</v>
+        <v>36.55401182724912</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01262412892690017</v>
+        <v>0.0133399658691226</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03219800531880384</v>
+        <v>0.2555509617068161</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03944634443023773</v>
+        <v>0.2855207962475916</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1363114274191036</v>
+        <v>27</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.3484886630260573</v>
       </c>
     </row>
     <row r="7">
@@ -587,7 +607,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02766228454924267</v>
+        <v>0.4907481236866402</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -595,7 +615,10 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.128151537093825</v>
+        <v>27</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.3625236241410573</v>
       </c>
     </row>
     <row r="8">
@@ -605,25 +628,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006547335284480371</v>
+        <v>0.4927224468618837</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001354784762765694</v>
+        <v>0.005164350114546849</v>
       </c>
       <c r="D8" t="n">
-        <v>2.013106596332452</v>
+        <v>82.32984474415368</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003828133865236785</v>
+        <v>0.005569354581411534</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003875961378623792</v>
+        <v>0.2118970918281774</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009218709190336922</v>
+        <v>0.2321908081802421</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1070365878290627</v>
+        <v>190</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.3644979473163008</v>
       </c>
     </row>
     <row r="9">
@@ -633,25 +659,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.005663458081302438</v>
+        <v>0.4944026783006348</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0004038476786903112</v>
+        <v>0.003493397020242982</v>
       </c>
       <c r="D9" t="n">
-        <v>2.007801262857778</v>
+        <v>83.08555910554423</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003200069840291781</v>
+        <v>0.004967326459374219</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004870232732261207</v>
+        <v>0.2172590992441865</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006456683430343787</v>
+        <v>0.2309584336657822</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1061527106258848</v>
+        <v>190</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.366178178755052</v>
       </c>
     </row>
     <row r="10">
@@ -661,25 +690,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00538792202197559</v>
+        <v>0.3116827501829642</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001322432247090697</v>
+        <v>0.005642934845880347</v>
       </c>
       <c r="D10" t="n">
-        <v>1.446163236959488</v>
+        <v>-2.784555456253408</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001607492108426603</v>
+        <v>0.002160043597944972</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002780996212260872</v>
+        <v>-0.02695490923714811</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007994847831690067</v>
+        <v>-0.004789596679334963</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1058771745665579</v>
+        <v>149</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1834582506373813</v>
       </c>
     </row>
     <row r="11">
@@ -689,7 +721,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02976530646511861</v>
+        <v>0.2740520270662675</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -697,7 +729,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.130254559009701</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1458275275206846</v>
       </c>
     </row>
     <row r="12">
@@ -707,7 +742,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04905868056158597</v>
+        <v>0.297564321026216</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -715,7 +750,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1495479331061683</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1693398214806331</v>
       </c>
     </row>
     <row r="13">
@@ -725,7 +763,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06538359255139212</v>
+        <v>0.3157540136348562</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -733,7 +771,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1658728450959744</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1875295140892733</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +784,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07006202855810219</v>
+        <v>0.3232492612406824</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -751,7 +792,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1705512811026845</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1950247616950995</v>
       </c>
     </row>
     <row r="15">
@@ -761,7 +805,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07633087236257265</v>
+        <v>0.3312043747198978</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -769,7 +813,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.176820124907155</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2029798751743149</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +826,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08097886877138172</v>
+        <v>0.3369147218743016</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -787,7 +834,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1814681213159641</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2086902223287187</v>
       </c>
     </row>
     <row r="17">
@@ -797,7 +847,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0836219187512979</v>
+        <v>0.3420475196341877</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -805,7 +855,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1841111712958802</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2138230200886048</v>
       </c>
     </row>
     <row r="18">
@@ -815,7 +868,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1004892525445823</v>
+        <v>0.1282244995455829</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
@@ -823,6 +876,9 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -833,7 +889,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08599450627814624</v>
+        <v>0.3453846111977491</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -841,7 +897,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1864837588227286</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2171601116521662</v>
       </c>
     </row>
     <row r="20">
@@ -851,7 +910,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08933997365639915</v>
+        <v>0.347198432611954</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -859,7 +918,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1898292262009815</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2189739330663711</v>
       </c>
     </row>
     <row r="21">
@@ -869,7 +931,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.09315002448509374</v>
+        <v>0.3515982303895668</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -877,7 +939,10 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1936392770296761</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.223373730843984</v>
       </c>
     </row>
     <row r="22">
@@ -887,25 +952,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0971558510159143</v>
+        <v>0.3568759092269637</v>
       </c>
       <c r="C22" t="n">
-        <v>0.00712795973837118</v>
+        <v>0.007133616849274649</v>
       </c>
       <c r="D22" t="n">
-        <v>24.00303453052241</v>
+        <v>24.02208455792759</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04304788334237448</v>
+        <v>0.04308204832915414</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08314390120397999</v>
+        <v>0.08320988842715776</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1111678008278485</v>
+        <v>0.1112560292412039</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1976451035604966</v>
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2286514096813808</v>
       </c>
     </row>
     <row r="23">
@@ -915,25 +983,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1010050028406189</v>
+        <v>0.3628116642691257</v>
       </c>
       <c r="C23" t="n">
-        <v>0.006997983110107142</v>
+        <v>0.007003537064956433</v>
       </c>
       <c r="D23" t="n">
-        <v>25.04201334668982</v>
+        <v>25.06188796045703</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03855730116383704</v>
+        <v>0.03858790219650675</v>
       </c>
       <c r="F23" t="n">
-        <v>0.08725576945402201</v>
+        <v>0.0873250200646998</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1147542362272157</v>
+        <v>0.1148453110178722</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2014942553852013</v>
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2345871647235428</v>
       </c>
     </row>
     <row r="24">
@@ -943,25 +1014,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1066304509128086</v>
+        <v>0.368591626480022</v>
       </c>
       <c r="C24" t="n">
-        <v>0.007222545988216703</v>
+        <v>0.007213686779037753</v>
       </c>
       <c r="D24" t="n">
-        <v>26.73009094960385</v>
+        <v>26.69430545250413</v>
       </c>
       <c r="E24" t="n">
-        <v>0.04262428682460107</v>
+        <v>0.04259211488343937</v>
       </c>
       <c r="F24" t="n">
-        <v>0.09243793987925054</v>
+        <v>0.09231226013733564</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1208229619463669</v>
+        <v>0.1206624707337614</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2071197034573909</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2403671269344392</v>
       </c>
     </row>
     <row r="25">
@@ -971,25 +1045,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1076398297490284</v>
+        <v>0.3709008954598699</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008307559260876866</v>
+        <v>0.008297423910843066</v>
       </c>
       <c r="D25" t="n">
-        <v>25.61670857916938</v>
+        <v>25.58187956638275</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04205968895953646</v>
+        <v>0.04202203914035453</v>
       </c>
       <c r="F25" t="n">
-        <v>0.09129675793533726</v>
+        <v>0.09115862516459486</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1239829015627198</v>
+        <v>0.1238049211483936</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2081290822936108</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2426763959142871</v>
       </c>
     </row>
     <row r="26">
@@ -999,25 +1076,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1094117248417065</v>
+        <v>0.3744942472704945</v>
       </c>
       <c r="C26" t="n">
-        <v>0.008106918617836153</v>
+        <v>0.008079142791037941</v>
       </c>
       <c r="D26" t="n">
-        <v>25.88901328842088</v>
+        <v>25.84170550539107</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0384221969316984</v>
+        <v>0.0383909162648128</v>
       </c>
       <c r="F26" t="n">
-        <v>0.09347302760122432</v>
+        <v>0.09321040364159139</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1253504220821886</v>
+        <v>0.1249786495037413</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2099009773862889</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2462697477249116</v>
       </c>
     </row>
     <row r="27">
@@ -1027,25 +1107,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1095168507379396</v>
+        <v>0.380470139431257</v>
       </c>
       <c r="C27" t="n">
-        <v>0.007016451903546652</v>
+        <v>0.007022020516168515</v>
       </c>
       <c r="D27" t="n">
-        <v>25.32383093340588</v>
+        <v>25.34392921192446</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0504331333752961</v>
+        <v>0.0504731596716257</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09572981411537045</v>
+        <v>0.09580579015831915</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1233038873605092</v>
+        <v>0.1234017475885731</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2100061032825219</v>
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2522456398856742</v>
       </c>
     </row>
     <row r="28">
@@ -1055,25 +1138,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1064955311289398</v>
+        <v>0.3823695608844331</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00690404387163713</v>
+        <v>0.006909523271535254</v>
       </c>
       <c r="D28" t="n">
-        <v>24.26027339296263</v>
+        <v>24.27952757819514</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08032228576350661</v>
+        <v>0.08038603360935066</v>
       </c>
       <c r="F28" t="n">
-        <v>0.09293077381063959</v>
+        <v>0.093004528393029</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1200602884472404</v>
+        <v>0.1201555743904525</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2069847836735222</v>
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2541450613388502</v>
       </c>
     </row>
     <row r="29">
@@ -1083,25 +1169,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.005810623435058298</v>
+        <v>0.3417249157968746</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0009589797129460442</v>
+        <v>0.001921433468894256</v>
       </c>
       <c r="D29" t="n">
-        <v>1.883611970712138</v>
+        <v>6.897173590080409</v>
       </c>
       <c r="E29" t="n">
-        <v>0.00338551360650741</v>
+        <v>0.01365820208876788</v>
       </c>
       <c r="F29" t="n">
-        <v>0.003920490647035675</v>
+        <v>0.01033711863439141</v>
       </c>
       <c r="G29" t="n">
-        <v>0.007700756223080829</v>
+        <v>0.01789861845310747</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1062998759796406</v>
+        <v>149</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2135004162512918</v>
       </c>
     </row>
   </sheetData>
